--- a/tests/ALiS_IndividualProfile_Baseline/baselines/View/NVRCP/Mammo.xlsx
+++ b/tests/ALiS_IndividualProfile_Baseline/baselines/View/NVRCP/Mammo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10668" windowHeight="9000" firstSheet="4" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9000" firstSheet="4"/>
   </bookViews>
   <sheets>
     <sheet name="TC01_Tabs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="89">
   <si>
     <t>Tab Name</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Home Address</t>
+  </si>
+  <si>
+    <t>Employment Details</t>
   </si>
   <si>
     <t>Violations</t>
@@ -1635,7 +1638,9 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1645,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1656,7 +1661,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1667,7 +1672,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1678,7 +1683,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1689,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1789,10 +1794,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -1809,10 +1814,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -1829,10 +1834,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -1849,10 +1854,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1869,10 +1874,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1889,10 +1894,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1909,10 +1914,10 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1929,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -1949,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -1969,10 +1974,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1989,10 +1994,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2009,10 +2014,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -2029,10 +2034,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -2049,10 +2054,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -2069,10 +2074,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -2089,10 +2094,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2109,10 +2114,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -2129,10 +2134,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -2149,10 +2154,10 @@
         <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -2169,10 +2174,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -2189,10 +2194,10 @@
         <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -2209,10 +2214,10 @@
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -2229,10 +2234,10 @@
         <v>10</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -2249,10 +2254,10 @@
         <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2269,10 +2274,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -2289,10 +2294,10 @@
         <v>10</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2306,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2326,13 +2331,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2346,13 +2351,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -2366,13 +2371,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -2386,13 +2391,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -2406,13 +2411,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -2426,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -2446,13 +2451,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -2466,13 +2471,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -2486,13 +2491,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -2506,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2520,13 +2525,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2553,10 +2558,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -2578,9 +2583,11 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2605,9 +2612,11 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -2633,10 +2642,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -2662,10 +2671,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -2691,10 +2700,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -2720,10 +2729,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -2749,10 +2758,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2">
         <v>5</v>
@@ -2778,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -2807,13 +2816,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -2836,13 +2845,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -2865,13 +2874,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2894,10 +2903,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2923,10 +2932,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2">
         <v>6</v>
@@ -2952,10 +2961,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" s="2">
         <v>7</v>
@@ -2981,10 +2990,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2">
         <v>8</v>
@@ -3010,13 +3019,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -3039,13 +3048,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -3068,13 +3077,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -3097,13 +3106,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -3126,13 +3135,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -3155,13 +3164,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -3184,10 +3193,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -3213,10 +3222,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -3242,10 +3251,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2">
         <v>3</v>
@@ -3271,10 +3280,10 @@
         <v>5</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" s="2">
         <v>4</v>
@@ -3300,10 +3309,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2">
         <v>5</v>
@@ -3329,10 +3338,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" s="2">
         <v>6</v>
@@ -3358,10 +3367,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -3387,10 +3396,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2">
         <v>8</v>
@@ -3416,10 +3425,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D31" s="2">
         <v>9</v>
@@ -3445,13 +3454,13 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -3474,13 +3483,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -3503,13 +3512,13 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -3532,13 +3541,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3561,13 +3570,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3590,13 +3599,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3619,10 +3628,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D38" s="2">
         <v>7</v>
@@ -3690,7 +3699,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" ht="55.2" spans="1:3">
@@ -3701,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
